--- a/VerveStacks_UZB_grids_kan15/vt_vervestacks_UZB_v1.xlsx
+++ b/VerveStacks_UZB_grids_kan15/vt_vervestacks_UZB_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_UZB_grids_kan15\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8D33F0B-FBA7-4D43-9510-CD746864F465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFF0495E-6CD0-4452-BE4A-5C9FC34A2E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{E92ACDD5-14C8-40D7-B6B1-D885CDCED720}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{09DA7C2B-5428-4C45-ADED-107AA73C61AE}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1972,11 +1972,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9936F922-5792-4820-A303-551C27E75C5D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{501FA01F-A810-4A0D-A2F7-B05C5AD3CC8E}">
   <dimension ref="B9:Y32"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>0</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="10" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="11" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>468</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="12" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>470</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="13" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>472</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="14" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>473</v>
       </c>
@@ -2309,7 +2309,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="15" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>475</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="16" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>477</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>479</v>
       </c>
@@ -2513,7 +2513,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>481</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>482</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>483</v>
       </c>
@@ -2717,7 +2717,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>484</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>485</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>486</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>487</v>
       </c>
@@ -2983,7 +2983,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>489</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>490</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>491</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="28" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>492</v>
       </c>
@@ -3237,7 +3237,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="29" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>493</v>
       </c>
@@ -3305,7 +3305,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="30" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>494</v>
       </c>
@@ -3367,7 +3367,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="31" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>496</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="32" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>497</v>
       </c>
@@ -3497,11 +3497,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{162E6DA0-EBA1-4432-AC1F-70A822D15CD2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1D75F17-EFA1-44EA-95A4-4483EDB1A479}">
   <dimension ref="B9:Y65"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>0</v>
       </c>
@@ -3509,7 +3509,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="10" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -3580,7 +3580,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="11" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>348</v>
       </c>
@@ -3645,7 +3645,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="12" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>349</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="13" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>350</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="14" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>351</v>
       </c>
@@ -3819,7 +3819,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="15" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>354</v>
       </c>
@@ -3878,7 +3878,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="16" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>355</v>
       </c>
@@ -3940,7 +3940,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>356</v>
       </c>
@@ -4002,7 +4002,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>357</v>
       </c>
@@ -4064,7 +4064,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>358</v>
       </c>
@@ -4126,7 +4126,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>359</v>
       </c>
@@ -4188,7 +4188,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>360</v>
       </c>
@@ -4250,7 +4250,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>361</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>362</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>363</v>
       </c>
@@ -4436,7 +4436,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>364</v>
       </c>
@@ -4498,7 +4498,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>366</v>
       </c>
@@ -4560,7 +4560,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>368</v>
       </c>
@@ -4622,7 +4622,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="28" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>369</v>
       </c>
@@ -4684,7 +4684,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="29" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>370</v>
       </c>
@@ -4746,7 +4746,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="30" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>372</v>
       </c>
@@ -4808,7 +4808,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="31" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>373</v>
       </c>
@@ -4870,7 +4870,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="32" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>374</v>
       </c>
@@ -4932,7 +4932,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>375</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>376</v>
       </c>
@@ -5056,7 +5056,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>377</v>
       </c>
@@ -5118,7 +5118,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="36" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>378</v>
       </c>
@@ -5180,7 +5180,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>379</v>
       </c>
@@ -5242,7 +5242,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>380</v>
       </c>
@@ -5304,7 +5304,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>382</v>
       </c>
@@ -5366,7 +5366,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>384</v>
       </c>
@@ -5428,7 +5428,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>386</v>
       </c>
@@ -5490,7 +5490,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>387</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>388</v>
       </c>
@@ -5614,7 +5614,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>389</v>
       </c>
@@ -5676,7 +5676,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>390</v>
       </c>
@@ -5738,7 +5738,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>391</v>
       </c>
@@ -5800,7 +5800,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>392</v>
       </c>
@@ -5862,7 +5862,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>393</v>
       </c>
@@ -5921,7 +5921,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="49" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>394</v>
       </c>
@@ -5980,7 +5980,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="50" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>395</v>
       </c>
@@ -6036,7 +6036,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="51" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>396</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="52" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>397</v>
       </c>
@@ -6148,7 +6148,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="53" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>398</v>
       </c>
@@ -6204,7 +6204,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="54" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>399</v>
       </c>
@@ -6263,7 +6263,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="55" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>400</v>
       </c>
@@ -6322,7 +6322,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="56" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>401</v>
       </c>
@@ -6381,7 +6381,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="57" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>402</v>
       </c>
@@ -6440,7 +6440,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="58" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>403</v>
       </c>
@@ -6499,7 +6499,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="59" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>404</v>
       </c>
@@ -6558,7 +6558,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="60" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>405</v>
       </c>
@@ -6620,7 +6620,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="61" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>406</v>
       </c>
@@ -6682,7 +6682,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="62" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>407</v>
       </c>
@@ -6744,7 +6744,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="63" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>408</v>
       </c>
@@ -6806,7 +6806,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>409</v>
       </c>
@@ -6868,7 +6868,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>410</v>
       </c>
@@ -6936,11 +6936,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54CDA24F-FA4C-49D3-8F4B-3380CE2B4A98}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16D911B2-987B-4E8F-A254-7A28C9638B78}">
   <dimension ref="B9:Y186"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>0</v>
       </c>
@@ -6948,7 +6948,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="10" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -7019,7 +7019,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="11" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>16</v>
       </c>
@@ -7078,7 +7078,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="12" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>20</v>
       </c>
@@ -7137,7 +7137,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="13" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>22</v>
       </c>
@@ -7196,7 +7196,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="14" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>23</v>
       </c>
@@ -7261,7 +7261,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="15" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>25</v>
       </c>
@@ -7326,7 +7326,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="16" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>27</v>
       </c>
@@ -7391,7 +7391,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>29</v>
       </c>
@@ -7456,7 +7456,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>31</v>
       </c>
@@ -7515,7 +7515,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>34</v>
       </c>
@@ -7574,7 +7574,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>35</v>
       </c>
@@ -7636,7 +7636,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>38</v>
       </c>
@@ -7698,7 +7698,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>40</v>
       </c>
@@ -7760,7 +7760,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>43</v>
       </c>
@@ -7825,7 +7825,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>46</v>
       </c>
@@ -7890,7 +7890,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>47</v>
       </c>
@@ -7955,7 +7955,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>48</v>
       </c>
@@ -8020,7 +8020,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>49</v>
       </c>
@@ -8085,7 +8085,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="28" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>50</v>
       </c>
@@ -8150,7 +8150,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="29" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>51</v>
       </c>
@@ -8215,7 +8215,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="30" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>52</v>
       </c>
@@ -8280,7 +8280,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="31" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>53</v>
       </c>
@@ -8345,7 +8345,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="32" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>54</v>
       </c>
@@ -8410,7 +8410,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>55</v>
       </c>
@@ -8475,7 +8475,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>56</v>
       </c>
@@ -8540,7 +8540,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>57</v>
       </c>
@@ -8599,7 +8599,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="36" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>59</v>
       </c>
@@ -8658,7 +8658,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>60</v>
       </c>
@@ -8723,7 +8723,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>61</v>
       </c>
@@ -8788,7 +8788,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>62</v>
       </c>
@@ -8847,7 +8847,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>64</v>
       </c>
@@ -8906,7 +8906,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>65</v>
       </c>
@@ -8965,7 +8965,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>66</v>
       </c>
@@ -9024,7 +9024,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>67</v>
       </c>
@@ -9089,7 +9089,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>68</v>
       </c>
@@ -9154,7 +9154,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>69</v>
       </c>
@@ -9213,7 +9213,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>71</v>
       </c>
@@ -9278,7 +9278,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>73</v>
       </c>
@@ -9337,7 +9337,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>74</v>
       </c>
@@ -9402,7 +9402,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="49" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>75</v>
       </c>
@@ -9467,7 +9467,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="50" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>76</v>
       </c>
@@ -9529,7 +9529,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="51" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>78</v>
       </c>
@@ -9591,7 +9591,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="52" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>79</v>
       </c>
@@ -9653,7 +9653,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="53" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>81</v>
       </c>
@@ -9715,7 +9715,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="54" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>82</v>
       </c>
@@ -9777,7 +9777,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="55" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>83</v>
       </c>
@@ -9839,7 +9839,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="56" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>84</v>
       </c>
@@ -9904,7 +9904,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="57" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>85</v>
       </c>
@@ -9969,7 +9969,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="58" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>86</v>
       </c>
@@ -10034,7 +10034,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="59" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>87</v>
       </c>
@@ -10099,7 +10099,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="60" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>88</v>
       </c>
@@ -10164,7 +10164,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="61" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>89</v>
       </c>
@@ -10229,7 +10229,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="62" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>90</v>
       </c>
@@ -10294,7 +10294,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="63" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>92</v>
       </c>
@@ -10359,7 +10359,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>93</v>
       </c>
@@ -10418,7 +10418,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>94</v>
       </c>
@@ -10483,7 +10483,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>95</v>
       </c>
@@ -10548,7 +10548,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>96</v>
       </c>
@@ -10613,7 +10613,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>97</v>
       </c>
@@ -10678,7 +10678,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>98</v>
       </c>
@@ -10743,7 +10743,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>99</v>
       </c>
@@ -10808,7 +10808,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>100</v>
       </c>
@@ -10873,7 +10873,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>101</v>
       </c>
@@ -10938,7 +10938,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>102</v>
       </c>
@@ -11003,7 +11003,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>103</v>
       </c>
@@ -11062,7 +11062,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
         <v>104</v>
       </c>
@@ -11121,7 +11121,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
         <v>105</v>
       </c>
@@ -11186,7 +11186,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
         <v>106</v>
       </c>
@@ -11251,7 +11251,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="78" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
         <v>107</v>
       </c>
@@ -11310,7 +11310,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
         <v>108</v>
       </c>
@@ -11369,7 +11369,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
         <v>109</v>
       </c>
@@ -11428,7 +11428,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="81" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
         <v>110</v>
       </c>
@@ -11487,7 +11487,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="82" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>111</v>
       </c>
@@ -11546,7 +11546,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="83" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
         <v>112</v>
       </c>
@@ -11605,7 +11605,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="84" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
         <v>113</v>
       </c>
@@ -11670,7 +11670,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="85" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
         <v>114</v>
       </c>
@@ -11735,7 +11735,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="86" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
         <v>115</v>
       </c>
@@ -11800,7 +11800,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="87" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
         <v>116</v>
       </c>
@@ -11865,7 +11865,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="88" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
         <v>117</v>
       </c>
@@ -11930,7 +11930,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="89" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
         <v>118</v>
       </c>
@@ -11995,7 +11995,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="90" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
         <v>119</v>
       </c>
@@ -12060,7 +12060,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="91" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
         <v>120</v>
       </c>
@@ -12125,7 +12125,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="92" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>121</v>
       </c>
@@ -12190,7 +12190,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="93" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
         <v>122</v>
       </c>
@@ -12255,7 +12255,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="94" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
         <v>123</v>
       </c>
@@ -12320,7 +12320,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="95" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
         <v>124</v>
       </c>
@@ -12370,7 +12370,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="96" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
         <v>126</v>
       </c>
@@ -12420,7 +12420,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="97" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
         <v>127</v>
       </c>
@@ -12470,7 +12470,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="98" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
         <v>129</v>
       </c>
@@ -12520,7 +12520,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="99" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
         <v>131</v>
       </c>
@@ -12570,7 +12570,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="100" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
         <v>132</v>
       </c>
@@ -12620,7 +12620,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="101" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
         <v>134</v>
       </c>
@@ -12679,7 +12679,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="102" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
         <v>135</v>
       </c>
@@ -12738,7 +12738,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="103" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
         <v>136</v>
       </c>
@@ -12797,7 +12797,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="104" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>137</v>
       </c>
@@ -12856,7 +12856,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="105" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
         <v>138</v>
       </c>
@@ -12915,7 +12915,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="106" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
         <v>139</v>
       </c>
@@ -12974,7 +12974,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="107" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
         <v>140</v>
       </c>
@@ -13033,7 +13033,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="108" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
         <v>141</v>
       </c>
@@ -13092,7 +13092,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="109" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
         <v>142</v>
       </c>
@@ -13151,7 +13151,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="110" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
         <v>144</v>
       </c>
@@ -13210,7 +13210,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="111" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
         <v>145</v>
       </c>
@@ -13269,7 +13269,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="112" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>146</v>
       </c>
@@ -13328,7 +13328,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="113" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
         <v>147</v>
       </c>
@@ -13387,7 +13387,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="114" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
         <v>148</v>
       </c>
@@ -13446,7 +13446,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="115" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>149</v>
       </c>
@@ -13499,7 +13499,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="116" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
         <v>149</v>
       </c>
@@ -13552,7 +13552,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="117" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
         <v>151</v>
       </c>
@@ -13605,7 +13605,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="118" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
         <v>151</v>
       </c>
@@ -13658,7 +13658,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="119" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
         <v>153</v>
       </c>
@@ -13711,7 +13711,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="120" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
         <v>153</v>
       </c>
@@ -13764,7 +13764,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="121" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
         <v>155</v>
       </c>
@@ -13817,7 +13817,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="122" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
         <v>155</v>
       </c>
@@ -13870,7 +13870,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="123" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
         <v>157</v>
       </c>
@@ -13923,7 +13923,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="124" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
         <v>157</v>
       </c>
@@ -13976,7 +13976,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="125" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
         <v>159</v>
       </c>
@@ -14029,7 +14029,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="126" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="126" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
         <v>159</v>
       </c>
@@ -14082,7 +14082,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="127" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="127" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>161</v>
       </c>
@@ -14135,7 +14135,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="128" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="128" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
         <v>161</v>
       </c>
@@ -14188,7 +14188,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="129" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
         <v>163</v>
       </c>
@@ -14241,7 +14241,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="130" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
         <v>163</v>
       </c>
@@ -14294,7 +14294,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="131" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
         <v>165</v>
       </c>
@@ -14347,7 +14347,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="132" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
         <v>165</v>
       </c>
@@ -14400,7 +14400,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="133" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
         <v>166</v>
       </c>
@@ -14453,7 +14453,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="134" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="134" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
         <v>166</v>
       </c>
@@ -14506,7 +14506,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="135" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="135" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
         <v>168</v>
       </c>
@@ -14559,7 +14559,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="136" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
         <v>168</v>
       </c>
@@ -14612,7 +14612,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="137" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
         <v>170</v>
       </c>
@@ -14665,7 +14665,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="138" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
         <v>172</v>
       </c>
@@ -14718,7 +14718,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="139" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
         <v>172</v>
       </c>
@@ -14771,7 +14771,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="140" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
         <v>174</v>
       </c>
@@ -14824,7 +14824,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="141" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
         <v>174</v>
       </c>
@@ -14877,7 +14877,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="142" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
         <v>176</v>
       </c>
@@ -14930,7 +14930,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="143" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
         <v>178</v>
       </c>
@@ -14983,7 +14983,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="144" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
         <v>178</v>
       </c>
@@ -15036,7 +15036,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="145" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
         <v>180</v>
       </c>
@@ -15089,7 +15089,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="146" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B146" t="s">
         <v>180</v>
       </c>
@@ -15142,7 +15142,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="147" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B147" t="s">
         <v>181</v>
       </c>
@@ -15195,7 +15195,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="148" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
         <v>181</v>
       </c>
@@ -15248,7 +15248,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="149" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B149" t="s">
         <v>183</v>
       </c>
@@ -15301,7 +15301,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="150" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="150" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
         <v>183</v>
       </c>
@@ -15354,7 +15354,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="151" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
         <v>185</v>
       </c>
@@ -15416,7 +15416,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="152" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="152" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
         <v>186</v>
       </c>
@@ -15478,7 +15478,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="153" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="153" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
         <v>187</v>
       </c>
@@ -15540,7 +15540,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="154" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="154" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
         <v>187</v>
       </c>
@@ -15602,7 +15602,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="155" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="155" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B155" t="s">
         <v>188</v>
       </c>
@@ -15664,7 +15664,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="156" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="156" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B156" t="s">
         <v>190</v>
       </c>
@@ -15726,7 +15726,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="157" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="157" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B157" t="s">
         <v>191</v>
       </c>
@@ -15788,7 +15788,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="158" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="158" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
         <v>191</v>
       </c>
@@ -15850,7 +15850,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="159" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="159" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
         <v>192</v>
       </c>
@@ -15888,7 +15888,7 @@
         <v>0.18243491148696719</v>
       </c>
     </row>
-    <row r="160" spans="2:25" x14ac:dyDescent="0.45">
+    <row r="160" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
         <v>192</v>
       </c>
@@ -15926,7 +15926,7 @@
         <v>0.18243491148696719</v>
       </c>
     </row>
-    <row r="161" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="161" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B161" t="s">
         <v>192</v>
       </c>
@@ -15964,7 +15964,7 @@
         <v>0.18243491148696719</v>
       </c>
     </row>
-    <row r="162" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="162" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B162" t="s">
         <v>193</v>
       </c>
@@ -16002,7 +16002,7 @@
         <v>0.18088058802679161</v>
       </c>
     </row>
-    <row r="163" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="163" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B163" t="s">
         <v>193</v>
       </c>
@@ -16040,7 +16040,7 @@
         <v>0.18088058802679158</v>
       </c>
     </row>
-    <row r="164" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="164" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B164" t="s">
         <v>193</v>
       </c>
@@ -16078,7 +16078,7 @@
         <v>0.18088058802679161</v>
       </c>
     </row>
-    <row r="165" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="165" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B165" t="s">
         <v>193</v>
       </c>
@@ -16116,7 +16116,7 @@
         <v>0.18088058802679161</v>
       </c>
     </row>
-    <row r="166" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="166" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B166" t="s">
         <v>194</v>
       </c>
@@ -16154,7 +16154,7 @@
         <v>0.18973025369144239</v>
       </c>
     </row>
-    <row r="167" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="167" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B167" t="s">
         <v>194</v>
       </c>
@@ -16192,7 +16192,7 @@
         <v>0.18973025369144242</v>
       </c>
     </row>
-    <row r="168" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="168" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B168" t="s">
         <v>194</v>
       </c>
@@ -16230,7 +16230,7 @@
         <v>0.18973025369144239</v>
       </c>
     </row>
-    <row r="169" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="169" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B169" t="s">
         <v>194</v>
       </c>
@@ -16268,7 +16268,7 @@
         <v>0.18973025369144239</v>
       </c>
     </row>
-    <row r="170" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="170" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B170" t="s">
         <v>195</v>
       </c>
@@ -16306,7 +16306,7 @@
         <v>0.18954867013696172</v>
       </c>
     </row>
-    <row r="171" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="171" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B171" t="s">
         <v>197</v>
       </c>
@@ -16344,7 +16344,7 @@
         <v>0.18540378689075079</v>
       </c>
     </row>
-    <row r="172" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="172" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B172" t="s">
         <v>198</v>
       </c>
@@ -16382,7 +16382,7 @@
         <v>0.19209914723490451</v>
       </c>
     </row>
-    <row r="173" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="173" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B173" t="s">
         <v>199</v>
       </c>
@@ -16420,7 +16420,7 @@
         <v>0.189720641448689</v>
       </c>
     </row>
-    <row r="174" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="174" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>201</v>
       </c>
@@ -16458,7 +16458,7 @@
         <v>0.1883268019654496</v>
       </c>
     </row>
-    <row r="175" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="175" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B175" t="s">
         <v>201</v>
       </c>
@@ -16496,7 +16496,7 @@
         <v>0.1883268019654496</v>
       </c>
     </row>
-    <row r="176" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="176" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B176" t="s">
         <v>202</v>
       </c>
@@ -16534,7 +16534,7 @@
         <v>0.18540378689075079</v>
       </c>
     </row>
-    <row r="177" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="177" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B177" t="s">
         <v>203</v>
       </c>
@@ -16572,7 +16572,7 @@
         <v>0.18540378689075079</v>
       </c>
     </row>
-    <row r="178" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="178" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B178" t="s">
         <v>204</v>
       </c>
@@ -16610,7 +16610,7 @@
         <v>0.189720641448689</v>
       </c>
     </row>
-    <row r="179" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="179" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>205</v>
       </c>
@@ -16648,7 +16648,7 @@
         <v>0.1883268019654496</v>
       </c>
     </row>
-    <row r="180" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="180" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B180" t="s">
         <v>206</v>
       </c>
@@ -16686,7 +16686,7 @@
         <v>0.18973025369144239</v>
       </c>
     </row>
-    <row r="181" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="181" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B181" t="s">
         <v>207</v>
       </c>
@@ -16724,7 +16724,7 @@
         <v>0.18088058802679161</v>
       </c>
     </row>
-    <row r="182" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="182" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B182" t="s">
         <v>208</v>
       </c>
@@ -16762,7 +16762,7 @@
         <v>0.18243491148696719</v>
       </c>
     </row>
-    <row r="183" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="183" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B183" t="s">
         <v>209</v>
       </c>
@@ -16800,7 +16800,7 @@
         <v>0.27613129179346979</v>
       </c>
     </row>
-    <row r="184" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="184" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B184" t="s">
         <v>211</v>
       </c>
@@ -16838,7 +16838,7 @@
         <v>0.27772136051586532</v>
       </c>
     </row>
-    <row r="185" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="185" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B185" t="s">
         <v>213</v>
       </c>
@@ -16876,7 +16876,7 @@
         <v>0.3154424544371402</v>
       </c>
     </row>
-    <row r="186" spans="2:16" x14ac:dyDescent="0.45">
+    <row r="186" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B186" t="s">
         <v>215</v>
       </c>
@@ -16920,9 +16920,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64616AE0-C1CC-44CA-98CB-62E115C279E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F7FD7A7-E3E7-4434-B3FD-21034DB4D8F7}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
